--- a/excelDataSource/20260610_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260610_涨停复盘_verified.xlsx
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>板块标题全部识别成功，各板块声明数量与提取股票数一致，自动校验通过。</t>
+          <t>03/04均识别成功，板块标题与声明数量校验通过。</t>
         </is>
       </c>
     </row>
